--- a/artfynd/A 38525-2025 artfynd.xlsx
+++ b/artfynd/A 38525-2025 artfynd.xlsx
@@ -1534,7 +1534,7 @@
         <v>126421048</v>
       </c>
       <c r="B9" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 38525-2025 artfynd.xlsx
+++ b/artfynd/A 38525-2025 artfynd.xlsx
@@ -1534,7 +1534,7 @@
         <v>126421048</v>
       </c>
       <c r="B9" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 38525-2025 artfynd.xlsx
+++ b/artfynd/A 38525-2025 artfynd.xlsx
@@ -1534,7 +1534,7 @@
         <v>126421048</v>
       </c>
       <c r="B9" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 38525-2025 artfynd.xlsx
+++ b/artfynd/A 38525-2025 artfynd.xlsx
@@ -1534,7 +1534,7 @@
         <v>126421048</v>
       </c>
       <c r="B9" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 38525-2025 artfynd.xlsx
+++ b/artfynd/A 38525-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,42 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>81142489</v>
+        <v>81142454</v>
       </c>
       <c r="B2" t="n">
-        <v>76909</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78350</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6437</v>
+        <v>314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>556689.1897918722</v>
+        <v>556720</v>
       </c>
       <c r="R2" t="n">
-        <v>6972758.962403609</v>
+        <v>6972699</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,21 +752,11 @@
           <t>2019-10-24</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2019-10-24</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -783,7 +768,7 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Torraka tall</t>
+          <t>Senvuxen gran i fuktigt läge</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -804,12 +789,7 @@
         <v>81142485</v>
       </c>
       <c r="B3" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -841,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>556703.8572345813</v>
+        <v>556704</v>
       </c>
       <c r="R3" t="n">
-        <v>6972730.011384133</v>
+        <v>6972730</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,19 +854,9 @@
           <t>2019-10-24</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2019-10-24</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -918,55 +888,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>81142490</v>
+        <v>81142450</v>
       </c>
       <c r="B4" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Storåsen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>556662.0102024096</v>
+        <v>556767</v>
       </c>
       <c r="R4" t="n">
-        <v>6972718.791143403</v>
+        <v>6972718</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,21 +956,11 @@
           <t>2019-10-24</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2019-10-24</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1022,7 +972,7 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Stående död gran</t>
+          <t>Granar i myrkant</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1040,15 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>81142454</v>
+        <v>81142489</v>
       </c>
       <c r="B5" t="n">
-        <v>76504</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1056,26 +1001,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>314</v>
+        <v>6437</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1089,10 +1034,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>556719.9349662767</v>
+        <v>556689</v>
       </c>
       <c r="R5" t="n">
-        <v>6972698.802923748</v>
+        <v>6972759</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1122,21 +1067,11 @@
           <t>2019-10-24</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2019-10-24</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1148,7 +1083,7 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Senvuxen gran i fuktigt läge</t>
+          <t>Torraka tall</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1166,15 +1101,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>81142453</v>
+        <v>81142486</v>
       </c>
       <c r="B6" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1182,31 +1112,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>cm²</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1215,10 +1145,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>556713.8079636991</v>
+        <v>556702</v>
       </c>
       <c r="R6" t="n">
-        <v>6972683.181324221</v>
+        <v>6972681</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1248,21 +1178,11 @@
           <t>2019-10-24</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2019-10-24</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1274,7 +1194,7 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Granlåga</t>
+          <t>Bark av gammal, senvuxen gran</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1292,15 +1212,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>81142486</v>
+        <v>81142493</v>
       </c>
       <c r="B7" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1341,10 +1256,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>556701.9617403341</v>
+        <v>556699</v>
       </c>
       <c r="R7" t="n">
-        <v>6972681.150760705</v>
+        <v>6972651</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1374,19 +1289,9 @@
           <t>2019-10-24</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2019-10-24</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1418,54 +1323,57 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>104451210</v>
+        <v>81142500</v>
       </c>
       <c r="B8" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bräcke, Jmt</t>
+          <t>Storåsen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>556568.5273157798</v>
+        <v>556572</v>
       </c>
       <c r="R8" t="n">
-        <v>6972522.314753836</v>
+        <v>6972406</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1489,22 +1397,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>13:43</t>
+          <t>2019-10-23</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>13:43</t>
+          <t>2019-10-23</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1515,61 +1413,66 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Sälg högstubbe</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Mattias Lif</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Mattias Lif</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126421048</v>
+        <v>81142487</v>
       </c>
       <c r="B9" t="n">
-        <v>57672</v>
+        <v>79583</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6459</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Brantbergtjärnen, Jmt</t>
+          <t>Storåsen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>556573</v>
+        <v>556656</v>
       </c>
       <c r="R9" t="n">
-        <v>6972681</v>
+        <v>6972758</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1596,17 +1499,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2019-10-24</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2019-10-24</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1617,19 +1515,449 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Senvuxen död myrgran</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
+          <t>Mattias Lif</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Mattias Lif</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>126421048</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Brantbergtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>556573</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6972681</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
           <t>Benny Öwre</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
+      <c r="AX10" t="inlineStr">
         <is>
           <t>Benny Öwre</t>
         </is>
       </c>
-      <c r="AY9" t="inlineStr"/>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>81142490</v>
+      </c>
+      <c r="B11" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Storåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>556662</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6972719</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2019-10-24</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2019-10-24</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Stående död gran</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Mattias Lif</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Mattias Lif</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>104451210</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Bräcke, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>556569</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6972522</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2022-10-31</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2022-10-31</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>104451211</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Bräcke, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>556527</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6972522</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2022-10-31</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2022-10-31</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 38525-2025 artfynd.xlsx
+++ b/artfynd/A 38525-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81142454</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -885,6 +895,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81142485</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -987,6 +1002,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81142450</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1098,6 +1118,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81142489</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1209,6 +1234,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81142486</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1320,6 +1350,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81142493</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1431,6 +1466,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81142500</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1533,6 +1573,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81142487</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1635,6 +1680,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126421048</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1742,6 +1792,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81142490</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1850,6 +1905,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104451210</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1958,8 +2018,27 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104451211</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>